--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130645206</v>
       </c>
       <c r="B4" t="n">
-        <v>75315</v>
+        <v>75317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130645206</v>
+        <v>130645210</v>
       </c>
       <c r="B4" t="n">
-        <v>75317</v>
+        <v>4779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667472</v>
+        <v>667485</v>
       </c>
       <c r="R4" t="n">
-        <v>6693360</v>
+        <v>6693332</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130645210</v>
+        <v>130645206</v>
       </c>
       <c r="B5" t="n">
-        <v>4779</v>
+        <v>75317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667485</v>
+        <v>667472</v>
       </c>
       <c r="R5" t="n">
-        <v>6693332</v>
+        <v>6693360</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1087,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130645210</v>
+        <v>130645206</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>75317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>667485</v>
+        <v>667472</v>
       </c>
       <c r="R4" t="n">
-        <v>6693332</v>
+        <v>6693360</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -970,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130645206</v>
+        <v>130645210</v>
       </c>
       <c r="B5" t="n">
-        <v>75317</v>
+        <v>4779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667472</v>
+        <v>667485</v>
       </c>
       <c r="R5" t="n">
-        <v>6693360</v>
+        <v>6693332</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,11 +1087,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130645206</v>
       </c>
       <c r="B4" t="n">
-        <v>75317</v>
+        <v>75325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130645206</v>
       </c>
       <c r="B4" t="n">
-        <v>75325</v>
+        <v>75326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>130645206</v>
       </c>
       <c r="B4" t="n">
-        <v>75326</v>
+        <v>75327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130645211</v>
+        <v>130645206</v>
       </c>
       <c r="B2" t="n">
-        <v>4779</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667484</v>
+        <v>667472</v>
       </c>
       <c r="R2" t="n">
-        <v>6693339</v>
+        <v>6693360</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +795,7 @@
         <v>130645209</v>
       </c>
       <c r="B3" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +907,7 @@
         <v>130645210</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130645206</v>
+        <v>130645211</v>
       </c>
       <c r="B5" t="n">
-        <v>75349</v>
+        <v>4781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667472</v>
+        <v>667484</v>
       </c>
       <c r="R5" t="n">
-        <v>6693360</v>
+        <v>6693339</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,11 +1087,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Senvuxen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
         <v>130645212</v>
       </c>
       <c r="B6" t="n">
-        <v>4779</v>
+        <v>4781</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61400-2025 artfynd.xlsx
+++ b/artfynd/A 61400-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645206</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645211</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130645212</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>